--- a/data/WP18_auswertung_abgeordnete.xlsx
+++ b/data/WP18_auswertung_abgeordnete.xlsx
@@ -2651,13 +2651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE84B3AF-1E2E-4FF3-B8D2-1638CE3D45E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D39E7E0-D01F-4410-BA8A-6166C8E103E2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F4C0E6-9589-46E4-B9C7-78CBE941EDC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDBE5966-0245-4A17-815C-449AC008B680}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7018F772-F2F1-47E7-933C-D466750DCF55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF0D58-BCD8-4395-8C38-705CC96A12F9}"/>
 </file>